--- a/Employee_Reports_wi52/Mario Dorado Hernandez Q0446.xlsx
+++ b/Employee_Reports_wi52/Mario Dorado Hernandez Q0446.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +475,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -569,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -829,53 +838,53 @@
       <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>AVI Equipment (CBF Trainings)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>CBF&amp;AVI</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>LSME-CBF-02-007</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>06-Oct-2024</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>06-Oct-2026</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -912,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1074,102 +1083,102 @@
       <c r="K13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-011</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>16-Aug-2025</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>16-Aug-2026</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-018</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>16-Aug-2025</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>16-Aug-2026</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1206,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1243,11 +1252,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1324,66 +1333,66 @@
       <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>22R1 Reefer Container</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>21-Nov-2024</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>48.83%</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
+      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Truck Dock 15Ft</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>30-Oct-2024</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>57.83%</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n"/>
+      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
